--- a/data/trans_orig/IP07C19-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07C19-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5732</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>6849</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10704</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>1884</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8566</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5080</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3141</t>
+          <t>2947</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10367</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7925</t>
+          <t>7960</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18914</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6213</t>
+          <t>6396</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>15903</t>
+          <t>16228</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>30457</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>12,95%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17118</t>
+          <t>16318</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13290</t>
+          <t>13387</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25915</t>
+          <t>26322</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,99%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>38292</t>
+          <t>38958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72662</t>
+          <t>73763</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>87799</t>
+          <t>88335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80729</t>
+          <t>81186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>95845</t>
+          <t>96977</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>65,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,62%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>158747</t>
+          <t>158771</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>180820</t>
+          <t>180568</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8109</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1356</t>
+          <t>1978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8396</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4716</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>14036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9429</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1322</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7562</t>
+          <t>8199</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4618</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13562</t>
+          <t>13768</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6984</t>
+          <t>7170</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18121</t>
+          <t>17977</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5812</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16617</t>
+          <t>15835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15377</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29438</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>15724</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30642</t>
+          <t>30749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10947</t>
+          <t>11071</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23017</t>
+          <t>23717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>29742</t>
+          <t>30062</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>48822</t>
+          <t>48844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125723</t>
+          <t>125538</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>144143</t>
+          <t>143976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,85%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>142478</t>
+          <t>142423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>159057</t>
+          <t>159179</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>273637</t>
+          <t>274858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298889</t>
+          <t>301041</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,1%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,62%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3206</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11622</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4238</t>
+          <t>3756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13297</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20377</t>
+          <t>20767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5025</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>9874</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9126</t>
+          <t>9618</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>21519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,59%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17798</t>
+          <t>17406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>33064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13821</t>
+          <t>14354</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27840</t>
+          <t>28262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>35430</t>
+          <t>35214</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>55641</t>
+          <t>56553</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25181</t>
+          <t>25600</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42930</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27740</t>
+          <t>27341</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>45978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>57842</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82446</t>
+          <t>82011</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>204744</t>
+          <t>204648</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>228519</t>
+          <t>227497</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>229238</t>
+          <t>229304</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>252661</t>
+          <t>251674</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>440002</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>472974</t>
+          <t>473442</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,96%</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2012 (tasa de respuesta: 95,41%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2012 (tasa de respuesta: 95,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6049</t>
+          <t>5978</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16531</t>
+          <t>16373</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>3288</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13206</t>
+          <t>12547</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11541</t>
+          <t>11612</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26309</t>
+          <t>24487</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11058</t>
+          <t>10622</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>24098</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7577</t>
+          <t>7555</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18745</t>
+          <t>18417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20736</t>
+          <t>20442</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>37852</t>
+          <t>38897</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9340</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20763</t>
+          <t>21307</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>16356</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>30829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28963</t>
+          <t>29340</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>48089</t>
+          <t>48736</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,04%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10510</t>
+          <t>10089</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>22523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>12291</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25852</t>
+          <t>25505</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26063</t>
+          <t>25748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>45557</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>83055</t>
+          <t>83253</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>103388</t>
+          <t>102874</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>82391</t>
+          <t>83118</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>102515</t>
+          <t>102430</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>171220</t>
+          <t>171199</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201638</t>
+          <t>199169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>65,55%</t>
         </is>
       </c>
     </row>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4400</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13163</t>
+          <t>14866</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>9,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3676</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12253</t>
+          <t>12354</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9932</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22036</t>
+          <t>22857</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7876</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18819</t>
+          <t>18809</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6912</t>
+          <t>7343</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>18026</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17948</t>
+          <t>17675</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32182</t>
+          <t>33046</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12129</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>26801</t>
+          <t>25585</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,77%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3952,12 +3952,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5043</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14909</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3967,12 +3967,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19698</t>
+          <t>20182</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36564</t>
+          <t>37232</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14221</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28801</t>
+          <t>28453</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>19336</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34533</t>
+          <t>34348</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4100,12 +4100,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37665</t>
+          <t>37331</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>57979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4115,12 +4115,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -4143,12 +4143,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92435</t>
+          <t>91983</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113532</t>
+          <t>112874</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4158,12 +4158,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4178,12 +4178,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>106155</t>
+          <t>106044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>126176</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4193,12 +4193,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4213,12 +4213,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>203896</t>
+          <t>201803</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>232123</t>
+          <t>231306</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,63%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12306</t>
+          <t>12525</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27242</t>
+          <t>26566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8535</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20362</t>
+          <t>20922</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24123</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>42486</t>
+          <t>42610</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36963</t>
+          <t>38341</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>17118</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32600</t>
+          <t>32860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42748</t>
+          <t>42685</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>65111</t>
+          <t>65996</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>24171</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>43942</t>
+          <t>42605</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24786</t>
+          <t>24127</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>41984</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54621</t>
+          <t>53695</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>79718</t>
+          <t>79208</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -4712,12 +4712,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27773</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>47350</t>
+          <t>47809</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4727,82 +4727,82 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
+          <t>15,32%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>44248</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>34761</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>56285</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>13,66%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>10,73%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>81005</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>67453</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>96516</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>12,74%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>10,61%</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
           <t>15,17%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>44248</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>34467</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>54612</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>13,66%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>16,86%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>81005</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>68065</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>94895</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>10,7%</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>14,92%</t>
         </is>
       </c>
     </row>
@@ -4825,12 +4825,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179607</t>
+          <t>177977</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>208362</t>
+          <t>208522</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -4840,12 +4840,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>66,8%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>194478</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>222868</t>
+          <t>223899</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>385962</t>
+          <t>383675</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>423736</t>
+          <t>424157</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>66,69%</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2016 (tasa de respuesta: 95,77%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2016 (tasa de respuesta: 95,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5285,12 +5285,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9408</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5300,12 +5300,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5320,12 +5320,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1329</t>
+          <t>1347</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8379</t>
+          <t>8577</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5335,12 +5335,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5355,12 +5355,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4546</t>
+          <t>4199</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>14551</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5370,12 +5370,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -5398,12 +5398,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6033</t>
+          <t>6038</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>16586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5433,12 +5433,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7875</t>
+          <t>7559</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19727</t>
+          <t>19261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5448,12 +5448,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5468,12 +5468,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>15739</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31234</t>
+          <t>30909</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5483,12 +5483,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -5511,12 +5511,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6432</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18086</t>
+          <t>18173</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5526,12 +5526,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5546,12 +5546,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>10982</t>
+          <t>12312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>25238</t>
+          <t>26140</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5561,12 +5561,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>21054</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23666</t>
+          <t>23268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39527</t>
+          <t>39801</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5639,12 +5639,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5659,12 +5659,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24696</t>
+          <t>24805</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>41938</t>
+          <t>41867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5694,12 +5694,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54195</t>
+          <t>52561</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>78202</t>
+          <t>76354</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,75%</t>
+          <t>21,24%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>111577</t>
+          <t>112290</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>133437</t>
+          <t>132864</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,77%</t>
+          <t>73,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>121719</t>
+          <t>122805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,76%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>218094</t>
+          <t>219145</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>247921</t>
+          <t>251173</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,87%</t>
         </is>
       </c>
     </row>
@@ -5967,12 +5967,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5982,12 +5982,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6002,12 +6002,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>13066</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6017,12 +6017,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6037,12 +6037,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>8922</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22306</t>
+          <t>22769</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,79%</t>
         </is>
       </c>
     </row>
@@ -6080,12 +6080,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4862</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15237</t>
+          <t>14954</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6095,12 +6095,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7020</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>17535</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6130,12 +6130,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6150,12 +6150,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28242</t>
+          <t>29385</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6165,12 +6165,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -6193,12 +6193,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>14061</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>5388</t>
+          <t>5426</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15751</t>
+          <t>16001</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>11562</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25905</t>
+          <t>25402</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -6306,12 +6306,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27168</t>
+          <t>26981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>44712</t>
+          <t>45490</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6321,12 +6321,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25639</t>
+          <t>25028</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43214</t>
+          <t>42611</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57004</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82141</t>
+          <t>83574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,92%</t>
         </is>
       </c>
     </row>
@@ -6419,12 +6419,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>93689</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114031</t>
+          <t>114664</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6434,12 +6434,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,66%</t>
+          <t>56,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>98720</t>
+          <t>98022</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119628</t>
+          <t>118909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6469,12 +6469,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,87%</t>
+          <t>57,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>199020</t>
+          <t>198012</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227423</t>
+          <t>227603</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6504,12 +6504,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,34%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -6649,12 +6649,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>7065</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18055</t>
+          <t>18749</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6684,12 +6684,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6328</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18694</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16570</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31805</t>
+          <t>32635</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -6762,12 +6762,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13244</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>28158</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6777,12 +6777,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17166</t>
+          <t>17392</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32807</t>
+          <t>32749</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6812,12 +6812,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>33543</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55273</t>
+          <t>54864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12712</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27257</t>
+          <t>27690</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6890,12 +6890,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>20370</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>37942</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6925,12 +6925,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36921</t>
+          <t>36745</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>59536</t>
+          <t>59438</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6960,12 +6960,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55409</t>
+          <t>55552</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>79304</t>
+          <t>79536</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7023,12 +7023,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53906</t>
+          <t>55592</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>79824</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7038,12 +7038,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7058,12 +7058,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>117663</t>
+          <t>118137</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>151282</t>
+          <t>152509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7073,12 +7073,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -7101,12 +7101,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>211873</t>
+          <t>213935</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240816</t>
+          <t>242492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7136,12 +7136,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>205872</t>
+          <t>203686</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>235914</t>
+          <t>233569</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7151,12 +7151,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7171,12 +7171,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>425035</t>
+          <t>427904</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>466564</t>
+          <t>469233</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7186,12 +7186,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>67,53%</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7366,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de burlarse de él otros chicos en 2023 (tasa de respuesta: 99,65%)</t>
+          <t>Menores según la frecuencia de burlarse de él otros/as chicos/as en 2023 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7566,7 +7566,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4158</t>
+          <t>4257</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7581,7 +7581,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7601,7 +7601,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5282</t>
+          <t>5552</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>738</t>
+          <t>847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>6915</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7646,12 +7646,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7679,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>4881</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7694,7 +7694,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>701</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7624</t>
+          <t>7535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7724,12 +7724,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>8717</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7759,12 +7759,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2110</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5094</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7842,7 +7842,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>320</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>4809</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7872,12 +7872,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -7900,12 +7900,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12748</t>
+          <t>12360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7915,12 +7915,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7935,12 +7935,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17797</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7950,12 +7950,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7970,12 +7970,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25967</t>
+          <t>25419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7985,12 +7985,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -8013,12 +8013,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>51900</t>
+          <t>51992</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>61903</t>
+          <t>62041</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8028,12 +8028,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8048,12 +8048,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>76180</t>
+          <t>76732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>89294</t>
+          <t>89728</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>77,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8083,12 +8083,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>131904</t>
+          <t>133077</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>149049</t>
+          <t>149221</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,85%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,2%</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5629</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>5845</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -8356,12 +8356,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1259</t>
+          <t>1237</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8851</t>
+          <t>8427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4508</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1967</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>10024</t>
+          <t>9859</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>523</t>
+          <t>532</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5749</t>
+          <t>6133</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8489,7 +8489,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>867</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8066</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2221</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,41%</t>
         </is>
       </c>
     </row>
@@ -8582,12 +8582,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2546</t>
+          <t>2683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>12205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8597,12 +8597,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8617,12 +8617,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6269</t>
+          <t>6776</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28848</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8632,12 +8632,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8652,12 +8652,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>11418</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38673</t>
+          <t>35471</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8667,12 +8667,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>11,29%</t>
         </is>
       </c>
     </row>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>121664</t>
+          <t>121583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>136082</t>
+          <t>136012</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8710,12 +8710,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8730,12 +8730,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140583</t>
+          <t>139051</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>162255</t>
+          <t>161406</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8745,12 +8745,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264503</t>
+          <t>267030</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293725</t>
+          <t>293727</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8780,7 +8780,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>701</t>
+          <t>687</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>6599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8945,7 +8945,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1516</t>
+          <t>1548</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9161</t>
+          <t>8897</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1825</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10392</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4937</t>
+          <t>4396</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15478</t>
+          <t>15845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1040</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6474</t>
+          <t>6064</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9125</t>
+          <t>8984</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12159</t>
+          <t>12569</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -9264,12 +9264,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7367</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20187</t>
+          <t>20743</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9279,12 +9279,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9299,12 +9299,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15753</t>
+          <t>15195</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9334,12 +9334,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26155</t>
+          <t>25725</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>55357</t>
+          <t>53869</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -9377,12 +9377,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>177918</t>
+          <t>177783</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>195923</t>
+          <t>195899</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9392,12 +9392,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>84,53%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9412,12 +9412,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>221063</t>
+          <t>223606</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247439</t>
+          <t>247473</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>82,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,32%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9447,12 +9447,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>406842</t>
+          <t>406394</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>439575</t>
+          <t>438341</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,05%</t>
         </is>
       </c>
     </row>
